--- a/data/trans_orig/IP41-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP41-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>143466</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>137514</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>146969</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>129645</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>124811</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>124143</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>132897</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>95,2%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>91,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>143466</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>137920</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>147345</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266735</t>
+          <t>266334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278776</t>
+          <t>278003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8286</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14238</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6533</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11367</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12035</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8286</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4407</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13832</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21195</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>151752</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>151752</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>151752</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136178</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136178</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136178</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>151752</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>151752</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>151752</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>199798</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>193670</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>204287</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>178838</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>171745</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>183915</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>172738</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>184052</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>91,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>199798</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>192413</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>204134</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>370090</t>
+          <t>370201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>386158</t>
+          <t>385300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11730</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17858</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>15671</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10594</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22764</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10457</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21771</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>8,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>11730</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>7394</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35948</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>211528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>211528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>211528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>194509</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>194509</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>194509</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>211528</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>211528</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>211528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>136221</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>130655</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>140471</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>124370</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>118405</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>128217</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>118465</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>128654</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>91,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>136221</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>130613</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>140448</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>92,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>253238</t>
+          <t>253099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266570</t>
+          <t>266829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10931</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6681</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16497</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10903</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7056</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16868</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6619</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>16808</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>8,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10931</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>16539</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>147152</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>147152</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>147152</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>135273</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>135273</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>135273</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>147152</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>147152</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>147152</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>181653</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>173668</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>187996</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>88,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>91,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>178620</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>168603</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>185641</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>169897</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>185904</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>87,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>181653</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>173003</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>187681</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>88,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>348188</t>
+          <t>348443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370894</t>
+          <t>370482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -1869,67 +1869,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>23555</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17212</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31540</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>26683</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19662</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>36700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19399</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35406</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23555</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>17527</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>32205</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>40029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62323</t>
+          <t>62068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205303</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205303</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205303</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>648186</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>672164</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>611473</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>597408</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>622663</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>598853</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>622097</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>661138</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>648998</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>671824</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1255897</t>
+          <t>1255890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1287529</t>
+          <t>1289194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>54502</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>43476</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>67454</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>59790</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>48600</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>73855</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>49166</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>72410</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,91%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>54502</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>43816</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>66642</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99374</t>
+          <t>97709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131006</t>
+          <t>131013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>671263</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>671263</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>671263</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>136434</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>128777</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>142074</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,2%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>128155</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>121397</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>132642</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>121210</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>132501</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>91,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>87,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>136434</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>129246</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>142492</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,2%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>255850</t>
+          <t>255066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>272330</t>
+          <t>271938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18250</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12610</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25907</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11202</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6715</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17960</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6856</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18147</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18250</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12192</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25438</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21711</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>205656</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>197517</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>211766</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>184441</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>177372</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>190364</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>177436</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>190905</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>89,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>85,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>205656</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>197446</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>211587</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>91,88%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>379773</t>
+          <t>379289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399059</t>
+          <t>399085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18179</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12069</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26318</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>21917</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15994</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28986</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15453</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>28922</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18179</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12248</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>26389</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31134</t>
+          <t>31108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50420</t>
+          <t>50904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,74 +3355,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>146428</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>138353</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>152296</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>87,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>138949</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>132756</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>132084</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>144169</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>89,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>85,4%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>93,22%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>146428</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>139079</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>152612</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>91,61%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>440</t>
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>276651</t>
+          <t>275840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293349</t>
+          <t>293238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20164</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14296</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28239</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15709</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>10489</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21902</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22574</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>10,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>6,78%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20164</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13980</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27513</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27901</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44599</t>
+          <t>45410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154658</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154658</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154658</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>176714</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>167907</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>185229</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>84,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>80,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>88,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>182179</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>173280</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>190127</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>173225</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>189803</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>86,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>176714</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>167051</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>184318</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>84,8%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>346122</t>
+          <t>345606</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370852</t>
+          <t>369949</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31682</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23167</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40489</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28121</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20173</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37020</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20497</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37075</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>31682</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24078</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>41345</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47844</t>
+          <t>48747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72574</t>
+          <t>73090</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>649247</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>679152</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>633723</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>620351</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>647122</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>619897</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>647022</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>89,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>87,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>665232</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>649515</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>678391</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1277477</t>
+          <t>1278637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1317922</t>
+          <t>1317666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>88275</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>74355</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104260</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>76950</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>63551</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>90322</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>63651</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>90776</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>88275</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>75116</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>103992</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146258</t>
+          <t>146514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>186703</t>
+          <t>185543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710673</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710673</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710673</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>136270</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>129632</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>141138</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>112643</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>104760</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>119313</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>105467</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>119018</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>84,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>136270</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>130099</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>141049</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237668</t>
+          <t>239039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256663</t>
+          <t>257155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11806</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18444</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21064</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14394</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28947</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14689</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28240</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>15,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7027</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17977</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44115</t>
+          <t>42744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>189359</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>179985</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>197221</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>177666</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>168210</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>184887</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>169368</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>184797</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>85,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>81,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>189359</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>180611</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>197512</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>84,4%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>353278</t>
+          <t>353676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>377714</t>
+          <t>377979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27138</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44374</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>29581</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22360</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39037</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>22450</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37879</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>14,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35000</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>26847</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>43748</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53892</t>
+          <t>53627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78328</t>
+          <t>77930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>129861</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>119912</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>138425</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>78,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>72,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>131177</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>123960</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>137455</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>123967</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>137555</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>84,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>129861</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>120099</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>138160</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249187</t>
+          <t>248549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>271487</t>
+          <t>271217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35526</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26962</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45475</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24820</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18542</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32037</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18442</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>32030</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>15,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35526</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27227</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>45288</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49897</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>72835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165387</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165387</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165387</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165387</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165387</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>167281</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>157438</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>176436</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>76,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>160724</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>179461</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>161089</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>180093</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>82,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>77,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>167281</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>157431</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>175421</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>81,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323541</t>
+          <t>323434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349991</t>
+          <t>351446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38455</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29300</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48298</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35730</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27058</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>45795</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>26426</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>45430</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>17,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38455</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>30315</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>48305</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>18,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62264</t>
+          <t>60809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88714</t>
+          <t>88821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206519</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206519</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>605446</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>638865</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>592276</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>576591</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>607939</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>574859</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>607310</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>84,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>81,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>622770</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>604626</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>638256</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1192569</t>
+          <t>1189699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1236573</t>
+          <t>1236418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120788</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>104693</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>138112</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>111194</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>95531</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>126879</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>96160</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128611</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>120788</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>105302</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>138932</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210455</t>
+          <t>210610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>254459</t>
+          <t>257329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>703470</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703470</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703470</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
